--- a/artfynd/A 38200-2021 artfynd.xlsx
+++ b/artfynd/A 38200-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38200-2021 artfynd.xlsx
+++ b/artfynd/A 38200-2021 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>89352671</v>
       </c>
       <c r="B2" t="n">
-        <v>89588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571967.178557481</v>
+        <v>571967</v>
       </c>
       <c r="R2" t="n">
-        <v>6620493.44672376</v>
+        <v>6620493</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +746,9 @@
           <t>2020-12-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-12-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,55 +790,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102312906</v>
+        <v>119623484</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>208257</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -861,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571953.0797047776</v>
+        <v>571953</v>
       </c>
       <c r="R3" t="n">
-        <v>6620464.412159506</v>
+        <v>6620464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,22 +868,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +898,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägren</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,52 +916,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119623484</v>
+        <v>102312906</v>
       </c>
       <c r="B4" t="n">
-        <v>56263</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1022,22 +997,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,7 +1017,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Vägren</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
